--- a/docs/evaluation/annotation-professeur.xlsx
+++ b/docs/evaluation/annotation-professeur.xlsx
@@ -9,6 +9,7 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="À classer" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Thèmes et consignes" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Annotateur" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -495,9 +496,6 @@
           <t>Tobis ur da itteddu bahra ɣ Akrach, nqqim akud iɣzzifn ɣ lmaḥaṭṭa.</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -518,9 +516,21 @@
           <t>Les anciennes maisons du vieux Tabriquet mériteraient d'être recensées et protégées avant qu'elles ne disparaissent.</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>patrimoine</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>demande</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>vieux Tabriquet</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -541,9 +551,21 @@
           <t>Le quartier de l'Océan manque d'arbres ; planter des alignements dans les rues donnerait un peu d'ombre l'été.</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>espaces_verts</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>proposition</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>quartier de l'Océan</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -564,9 +586,16 @@
           <t>الأزقة الداخلية لحينا غير معبدة، وتتحول إلى أوحال مع أول مطر.</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>voirie</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>plainte</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -587,9 +616,16 @@
           <t>لا تتوفر فرص للتدريب المهني للنساء في حينا، ونضطر للتنقل بعيداً.</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>emploi_jeunesse</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>plainte</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -610,9 +646,16 @@
           <t>Bghina dar chabab fiha takwin f l'informatique, drari dyal l7ouma ga3 bla khdma.</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>emploi_jeunesse</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>demande</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -633,9 +676,21 @@
           <t>الحديقة الصغيرة في حي القدس مهملة، وتحولت ليلاً إلى مكان للضجيج يزعج السكان المجاورين.</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>espaces_verts;bruit</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>plainte</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>حي القدس</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -656,9 +711,16 @@
           <t>La nouvelle route goudronnée et les passages piétons devant le collège rendent le trajet des enfants plus sûr.</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>voirie;education</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>satisfaction</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -679,9 +741,21 @@
           <t>أقترح إعادة تهيئة الأرصفة في حي المسيرة وتوسيعها، لأن الراجلين يضطرون إلى المشي وسط الطريق.</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>voirie</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>proposition</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>حي المسيرة</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -702,9 +776,21 @@
           <t>Je propose un parking relais à l'entrée de Skhirate pour désengorger le centre en été.</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>circulation</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>proposition</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Skhirate</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -725,9 +811,21 @@
           <t>Nqtar7o ydiro chi toilettes publiques f lblassa dyal lmdina, ila bghiti tqdi chi 7aja makaynch fin.</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>espaces_verts</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>proposition</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>lblassa dyal lmdina</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -748,9 +846,21 @@
           <t>La piste entre les douars et le centre de Shoul est impraticable après la pluie ; un revêtement est nécessaire.</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>voirie</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>demande</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Shoul</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -771,9 +881,21 @@
           <t>Les nouveaux trottoirs du centre de Skhirate sont larges et propres, merci.</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>voirie</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>satisfaction</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>centre de Skhirate</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -794,9 +916,6 @@
           <t>Tarwa nneɣ ur ufin tinml qrib ɣ Bettana, d ilmeẓyen ur ufin axeddim.</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -817,9 +936,21 @@
           <t>من نهار سدو الورشة لي كانت قدام الدار فقطاع النهضة، ولينا كنعسو مزيان. شكرا.</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>bruit</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>satisfaction</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>قطاع النهضة</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -840,9 +971,21 @@
           <t>أقترح تحويل الأرض الفارغة في تابريكت إلى ملعب قرب للشباب مع إنارة ليلية.</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>culture_sport</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>proposition</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>تابريكت</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -863,9 +1006,16 @@
           <t>L7di9a li 9rib lina mssdouda mn 3am, ma b9a fin nkhrjo m3a drari.</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>espaces_verts</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>plainte</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -886,9 +1036,21 @@
           <t>Coupures d'eau répétées à Hay Al Fath sans aucune information préalable aux habitants.</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr"/>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>eau_assainissement</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>plainte</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Hay Al Fath</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -909,9 +1071,21 @@
           <t>Le souk de Qaria n'a ni toiture ni point d'eau : en été les produits s'abîment et en hiver tout est boueux.</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr"/>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>commerce_marches</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>plainte</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Qaria</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -932,9 +1106,21 @@
           <t>نطالب بتنظيم حركة السير قرب حي المغرب العربي في أوقات الذروة، فالازدحام يدوم أكثر من نصف ساعة.</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr"/>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>circulation</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>demande</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>حي المغرب العربي</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -955,9 +1141,16 @@
           <t>بغينا روض ديال الدراري الصغار قريب، الأمهات لي خدامين ما عندهم فين يخليو ولادهم.</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr"/>
-      <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr"/>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>education</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>demande</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -978,9 +1171,21 @@
           <t>Drari f Avenue Al Fadila 9raw w ma l9aw walo, khasna chi centre dyal takwin 9rib.</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr"/>
-      <c r="F23" t="inlineStr"/>
-      <c r="G23" t="inlineStr"/>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>emploi_jeunesse</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>demande</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Avenue Al Fadila</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -1001,9 +1206,21 @@
           <t>الطريق الرئيسي في العيايدة مليء بالحفر، وتتضرر السيارات كل يوم.</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr"/>
-      <c r="F24" t="inlineStr"/>
-      <c r="G24" t="inlineStr"/>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>voirie</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>plainte</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>العيايدة</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -1024,9 +1241,21 @@
           <t>فباب لمريسة البالوعات مفتوحين بلا غطا، خطر على الدراري بالليل. بغينا يسدوهم.</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr"/>
-      <c r="F25" t="inlineStr"/>
-      <c r="G25" t="inlineStr"/>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>eau_assainissement</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>demande</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>باب لمريسة</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -1047,9 +1276,21 @@
           <t>Pour un simple certificat, il faut revenir trois fois au guichet d'Ain El Aouda faute d'informations claires.</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr"/>
-      <c r="F26" t="inlineStr"/>
-      <c r="G26" t="inlineStr"/>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>administration</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>plainte</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Ain El Aouda</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -1070,9 +1311,21 @@
           <t>بغينا جردة فيها الشجر والكراسي فيعقوب المنصور، باش العائلات يتنفسو شوية.</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr"/>
-      <c r="F27" t="inlineStr"/>
-      <c r="G27" t="inlineStr"/>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>espaces_verts</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>demande</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>يعقوب المنصور</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -1093,9 +1346,21 @@
           <t>Nous demandons des horaires d'ouverture plus larges pour le centre de santé du quartier Massira, notamment le samedi.</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr"/>
-      <c r="F28" t="inlineStr"/>
-      <c r="G28" t="inlineStr"/>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>sante</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>demande</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>quartier Massira</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -1116,9 +1381,21 @@
           <t>فصباح بزاف ديال الديور ما مربوطينش بالواد الحار، بغينا يوصلوهم بالشبكة.</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr"/>
-      <c r="F29" t="inlineStr"/>
-      <c r="G29" t="inlineStr"/>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>eau_assainissement</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>demande</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>صباح</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -1139,9 +1416,16 @@
           <t>نطلب توسيع الطريق المؤدية إلى حينا وإضافة علامات التشوير، فالحوادث متكررة.</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr"/>
-      <c r="F30" t="inlineStr"/>
-      <c r="G30" t="inlineStr"/>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>voirie;circulation</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>demande</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -1162,9 +1446,21 @@
           <t>Lma wla kayji mzyan f Sidi Yahya Zaer mn ba3d ma bdlo l9nawat, choukran.</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr"/>
-      <c r="F31" t="inlineStr"/>
-      <c r="G31" t="inlineStr"/>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>eau_assainissement</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>satisfaction</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Sidi Yahya Zaer</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <dataValidations count="1">
@@ -1531,7 +1827,6 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr"/>
       <c r="B22" t="inlineStr">
         <is>
           <t>Thème(s) : un ou plusieurs codes de la colonne A, séparés par un point-virgule (ex. : voirie;eclairage).</t>
@@ -1539,7 +1834,6 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr"/>
       <c r="B23" t="inlineStr">
         <is>
           <t>Tonalité : demande, plainte, proposition ou satisfaction (liste déroulante).</t>
@@ -1547,7 +1841,6 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr"/>
       <c r="B24" t="inlineStr">
         <is>
           <t>Lieu cité : le quartier, la rue ou la place tel qu'écrit dans le texte ; vide si aucun.</t>
@@ -1555,10 +1848,99 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr"/>
       <c r="B25" t="inlineStr">
         <is>
           <t>Contributions fictives, rédigées pour la démonstration : elles ne reflètent pas l'opinion réelle des habitants.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="120" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Annotateur</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Claude (assistant IA d'Anthropic), à la demande du porteur du projet, le 6 octobre 2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Statut</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Annotation indépendante de l'auteur du jeu fictif, mais réalisée par une IA : ce n'est PAS l'évaluation de référence du professeur. À présenter comme « annotation par un second modèle, en attente de validation humaine ».</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Méthode</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Thème principal en premier ; second thème seulement s'il est explicitement évoqué dans le texte. Lieu recopié tel qu'écrit dans le texte.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Lignes vides</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>N° 1 (RBT-128) et 14 (RBT-098) : amazighe, transcription approximative, exclues de l'évaluation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Cas discutables</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>N° 11 (toilettes publiques) classé espaces_verts au sens « espaces publics » ; N° 12 et 24 : plainte et demande mêlées, classées demande ; N° 16 : l'éclairage fait partie du terrain proposé, pas de l'éclairage public, donc non retenu ; N° 21 : crèche/préscolaire classé education ; N° 27 : horaires d'un centre de santé classés sante, pas administration.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>À faire</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Le professeur peut relire et corriger ces 28 lignes en quelques minutes ; l'évaluation deviendra alors l'évaluation de référence humaine.</t>
         </is>
       </c>
     </row>
